--- a/src/main/resources/excel-template/用户信息.xlsx
+++ b/src/main/resources/excel-template/用户信息.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>用户名</t>
   </si>
@@ -45,6 +45,18 @@
   </si>
   <si>
     <t>川A12346</t>
+  </si>
+  <si>
+    <t>lhw</t>
+  </si>
+  <si>
+    <t>川A12347</t>
+  </si>
+  <si>
+    <t>lll</t>
+  </si>
+  <si>
+    <t>川A12348</t>
   </si>
 </sst>
 </file>
@@ -1234,8 +1246,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="2" width="10" customWidth="1"/>
   </cols>
@@ -1264,6 +1276,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/src/main/resources/excel-template/用户信息.xlsx
+++ b/src/main/resources/excel-template/用户信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="住户信息" sheetId="1" r:id="rId1"/>
